--- a/Hansen_green_calculator/PlottedInks.xlsx
+++ b/Hansen_green_calculator/PlottedInks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a4263\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BC9122-6807-4042-8172-5EE5E8B9D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82E6A5A-3AF7-4D97-BA98-C801014E6E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{326D9CA9-DCE2-4417-841B-8A5822E8129E}"/>
+    <workbookView xWindow="7930" yWindow="470" windowWidth="9800" windowHeight="7270" activeTab="1" xr2:uid="{326D9CA9-DCE2-4417-841B-8A5822E8129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Solvents" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>D</t>
   </si>
@@ -97,6 +97,33 @@
   </si>
   <si>
     <t>CsFAPbI3</t>
+  </si>
+  <si>
+    <t>Keely</t>
+  </si>
+  <si>
+    <t>YanYan</t>
+  </si>
+  <si>
+    <t>DMSO(0.28)-ACN(13)-EtOH(34)-MeTHF(25)</t>
+  </si>
+  <si>
+    <t>DMSO(0.425)-ACN(0.075)-EtOH(0.075)-MeTHF(0.425)</t>
+  </si>
+  <si>
+    <t>Solvents</t>
+  </si>
+  <si>
+    <t>MABrMAClCsIPbBr2PbI2FAl</t>
+  </si>
+  <si>
+    <t>DMSO(0.2)-DMF(0.8)</t>
+  </si>
+  <si>
+    <t>ACN(0.45)-2ME(0.46)-DMS(0.09)</t>
+  </si>
+  <si>
+    <t>Acetaldehyde(0.68)-2ME(0.32)</t>
   </si>
 </sst>
 </file>
@@ -1107,10 +1134,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E6983A-F85F-4DE5-8AC9-7FD7AFF7E859}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1126,8 +1153,11 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1147,7 +1177,7 @@
         <v>13.314999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1167,7 +1197,7 @@
         <v>12.02</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1187,7 +1217,7 @@
         <v>6.9949999999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1195,19 +1225,16 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <f>(0.46*Solvents!B6)+(0.46*Solvents!B7)+(0.08*Solvents!B9)</f>
-        <v>15.516000000000002</v>
+        <v>12.11</v>
       </c>
       <c r="D5">
-        <f>(0.46*Solvents!C6)+(0.46*Solvents!C7)+(0.08*Solvents!C9)</f>
-        <v>10.830000000000002</v>
+        <v>11.33</v>
       </c>
       <c r="E5">
-        <f>(0.46*Solvents!D6)+(0.46*Solvents!D7)+(0.08*Solvents!D9)</f>
-        <v>5.0640000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1215,16 +1242,113 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <f>(0.46*Solvents!B6)+(0.46*Solvents!B7)+(0.08*Solvents!B9)</f>
-        <v>15.516000000000002</v>
+        <v>12.11</v>
       </c>
       <c r="D6">
-        <f>(0.46*Solvents!C6)+(0.46*Solvents!C7)+(0.08*Solvents!C9)</f>
-        <v>10.830000000000002</v>
+        <v>11.33</v>
       </c>
       <c r="E6">
-        <f>(0.46*Solvents!D6)+(0.46*Solvents!D7)+(0.08*Solvents!D9)</f>
-        <v>5.0640000000000001</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>12.12</v>
+      </c>
+      <c r="D7">
+        <v>11.23</v>
+      </c>
+      <c r="E7">
+        <v>7.33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>12.5</v>
+      </c>
+      <c r="D8">
+        <v>9.9</v>
+      </c>
+      <c r="E8">
+        <v>7.9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>16.5</v>
+      </c>
+      <c r="D9">
+        <v>13.5</v>
+      </c>
+      <c r="E9">
+        <v>10.4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>16.5</v>
+      </c>
+      <c r="D10">
+        <v>13.5</v>
+      </c>
+      <c r="E10">
+        <v>10.4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>18.21</v>
+      </c>
+      <c r="D12">
+        <v>11.23</v>
+      </c>
+      <c r="E12">
+        <v>7.7850000000000001</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
